--- a/artfynd/A 60240-2025 artfynd.xlsx
+++ b/artfynd/A 60240-2025 artfynd.xlsx
@@ -1526,7 +1526,7 @@
         <v>129688154</v>
       </c>
       <c r="B10" t="n">
-        <v>97667</v>
+        <v>97671</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1632,7 +1632,7 @@
         <v>129688155</v>
       </c>
       <c r="B11" t="n">
-        <v>98790</v>
+        <v>98794</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1735,10 +1735,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129688158</v>
+        <v>129688157</v>
       </c>
       <c r="B12" t="n">
-        <v>79081</v>
+        <v>91623</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1746,21 +1746,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1774,10 +1774,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>514579</v>
+        <v>514576</v>
       </c>
       <c r="R12" t="n">
-        <v>6938978</v>
+        <v>6938976</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1841,10 +1841,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129688157</v>
+        <v>129688158</v>
       </c>
       <c r="B13" t="n">
-        <v>91620</v>
+        <v>79084</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1852,21 +1852,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1880,10 +1880,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>514576</v>
+        <v>514579</v>
       </c>
       <c r="R13" t="n">
-        <v>6938976</v>
+        <v>6938978</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>

--- a/artfynd/A 60240-2025 artfynd.xlsx
+++ b/artfynd/A 60240-2025 artfynd.xlsx
@@ -1526,7 +1526,7 @@
         <v>129688154</v>
       </c>
       <c r="B10" t="n">
-        <v>97671</v>
+        <v>97674</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1632,7 +1632,7 @@
         <v>129688155</v>
       </c>
       <c r="B11" t="n">
-        <v>98794</v>
+        <v>98797</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1738,7 +1738,7 @@
         <v>129688157</v>
       </c>
       <c r="B12" t="n">
-        <v>91623</v>
+        <v>91626</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1844,7 +1844,7 @@
         <v>129688158</v>
       </c>
       <c r="B13" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 60240-2025 artfynd.xlsx
+++ b/artfynd/A 60240-2025 artfynd.xlsx
@@ -1526,7 +1526,7 @@
         <v>129688154</v>
       </c>
       <c r="B10" t="n">
-        <v>97674</v>
+        <v>97675</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1632,7 +1632,7 @@
         <v>129688155</v>
       </c>
       <c r="B11" t="n">
-        <v>98797</v>
+        <v>98798</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1735,10 +1735,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129688157</v>
+        <v>129688158</v>
       </c>
       <c r="B12" t="n">
-        <v>91626</v>
+        <v>79088</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1746,21 +1746,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1774,10 +1774,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>514576</v>
+        <v>514579</v>
       </c>
       <c r="R12" t="n">
-        <v>6938976</v>
+        <v>6938978</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1841,10 +1841,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129688158</v>
+        <v>129688157</v>
       </c>
       <c r="B13" t="n">
-        <v>79087</v>
+        <v>91627</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1852,21 +1852,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1880,10 +1880,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>514579</v>
+        <v>514576</v>
       </c>
       <c r="R13" t="n">
-        <v>6938978</v>
+        <v>6938976</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>

--- a/artfynd/A 60240-2025 artfynd.xlsx
+++ b/artfynd/A 60240-2025 artfynd.xlsx
@@ -1735,10 +1735,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129688158</v>
+        <v>129688157</v>
       </c>
       <c r="B12" t="n">
-        <v>79088</v>
+        <v>91627</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1746,21 +1746,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1774,10 +1774,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>514579</v>
+        <v>514576</v>
       </c>
       <c r="R12" t="n">
-        <v>6938978</v>
+        <v>6938976</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1841,10 +1841,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129688157</v>
+        <v>129688158</v>
       </c>
       <c r="B13" t="n">
-        <v>91627</v>
+        <v>79088</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1852,21 +1852,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1880,10 +1880,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>514576</v>
+        <v>514579</v>
       </c>
       <c r="R13" t="n">
-        <v>6938976</v>
+        <v>6938978</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>

--- a/artfynd/A 60240-2025 artfynd.xlsx
+++ b/artfynd/A 60240-2025 artfynd.xlsx
@@ -1526,7 +1526,7 @@
         <v>129688154</v>
       </c>
       <c r="B10" t="n">
-        <v>97675</v>
+        <v>97692</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1632,7 +1632,7 @@
         <v>129688155</v>
       </c>
       <c r="B11" t="n">
-        <v>98798</v>
+        <v>98815</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1738,7 +1738,7 @@
         <v>129688157</v>
       </c>
       <c r="B12" t="n">
-        <v>91627</v>
+        <v>91644</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1844,7 +1844,7 @@
         <v>129688158</v>
       </c>
       <c r="B13" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 60240-2025 artfynd.xlsx
+++ b/artfynd/A 60240-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY16"/>
+  <dimension ref="A1:AZ16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -778,6 +783,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129001005</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -884,6 +894,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129688157</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -990,6 +1005,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129688158</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1096,6 +1116,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127415120</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1202,6 +1227,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127415121</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1308,6 +1338,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127415122</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1414,6 +1449,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127415125</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1520,6 +1560,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129688156</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1626,6 +1671,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127415075</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1732,6 +1782,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127415123</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1838,6 +1893,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127415126</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1944,6 +2004,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129688155</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2050,6 +2115,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127415124</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2156,6 +2226,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129688154</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2262,8 +2337,30 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127415128</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>